--- a/data/trans_orig/IP31KM14_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM14_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20767</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13923</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30750</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19586</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13474</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28550</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46220</t>
+          <t>42213</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>31286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63187</t>
+          <t>54530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>102129</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92146</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>108973</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>94665</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85701</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100777</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>110182</t>
+          <t>97152</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93765</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119532</t>
+          <t>103954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>204846</t>
+          <t>199281</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187879</t>
+          <t>186964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217027</t>
+          <t>210208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41819</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31565</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>54632</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30477</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22402</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40222</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57153</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73932</t>
+          <t>70936</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59611</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>86014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>189422</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>176609</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>199676</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>155637</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>145892</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>163712</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>204065</t>
+          <t>151475</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190367</t>
+          <t>142985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213306</t>
+          <t>158680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>359702</t>
+          <t>340897</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344152</t>
+          <t>325819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>374023</t>
+          <t>353617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25048</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44107</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>23190</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13597</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34800</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45940</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59140</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43137</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74744</t>
+          <t>65550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133499</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122415</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141474</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>165059</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153449</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>174652</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147139</t>
+          <t>134212</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137149</t>
+          <t>125881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157127</t>
+          <t>140174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>312199</t>
+          <t>267712</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>296595</t>
+          <t>256010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328202</t>
+          <t>279189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32247</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23730</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41437</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40927</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>31819</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51043</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40806</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32083</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50563</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35172</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25590</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45962</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>73053</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62676</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>85815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>133918</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124728</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142435</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>123592</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>113476</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>132700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>123173</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>113416</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>131896</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>142137</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>131347</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>151719</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,16%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>265729</t>
+          <t>257091</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250388</t>
+          <t>244329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279152</t>
+          <t>269075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>127855</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>110698</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>148862</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>114180</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>94435</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>134058</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120956</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168997</t>
+          <t>129370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>240050</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226784</t>
+          <t>215056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288156</t>
+          <t>265890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>558969</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>537962</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>576126</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>758</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>538954</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>519076</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>558699</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>603523</t>
+          <t>506013</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>575736</t>
+          <t>488838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>623777</t>
+          <t>522852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1142477</t>
+          <t>1064981</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1109711</t>
+          <t>1039141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1171083</t>
+          <t>1089975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
